--- a/data_extactor/batch_10_fa/trimmed/batch_0062_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0062_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | فروش و بازاریابی | امور اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فروش و بازاریابی | اداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>راهنمایان تشریفات و خدمات هتل | کارشناسان خدمات مشتریان | مدیران مراکز اقامتی و هتل‌ها | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | کارشناسان و راهنمایان طبیعت‌شناسی پارک‌ها | متصدیان صدور بلیت و کارمندان رزرواسیون سفر | راهنمایان تور و همراهان گردشگران</t>
+          <t>متصدیان تشریفات و خدمات میهمانان | کارشناسان خدمات و پشتیبانی مشتریان | مدیران هتل و مراکز اقامتی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | طبیعت‌شناسان و کارشناسان پارک‌های ملی | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | راهنمایان تور و گردشگری</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نگارش | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | آموزش و تدریس | ایمنی و امنیت عمومی | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مدیران مراکز پیش‌دبستانی و مهدکودک‌ها | آموزگاران دوره آمادگی و مهدکودک | پرستاران خانگی و دایه‌ها | مراقبان خدمات فردی | مربیان پیش‌دبستانی | کمک‌آموزگاران مدارس</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | پرستاران خانگی و دایه‌ها | مراقبان خدمات شخصی و همراهان توان‌خواهان | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نگارش | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | روان‌شناسی | آموزش و تدریس | ایمنی و امنیت عمومی</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | آموزش و پرورش | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مربیان و مراقبان کودک | مراقبان سلامت در منزل | آموزگاران دوره آمادگی و مهدکودک | مراقبان خدمات فردی | مربیان پیش‌دبستانی | مربیان و سرپرستان خوابگاه</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مربیان و مراقبان کودک | مراقبان سلامت و بهیاران مراقبت در منزل | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | مراقبان خدمات شخصی و همراهان توان‌خواهان | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | سرپرستان و مشاوران خوابگاه</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | راهبردهای یادگیری | نظارت | یادگیری فعال | تفکر انتقادی | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | راهبردهای یادگیری | نظارت | یادگیری فعال | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | آموزش و تدریس | زبان انگلیسی | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | زبان انگلیسی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>استقامت بدنی | انعطاف‌پذیری عمومی بدن | هماهنگی کلی اعضای بدن | بیان شفاهی | قدرت تنه | وضوح گفتار | درک شفاهی</t>
+          <t>استقامت | انعطاف‌پذیری دامنه حرکت | هماهنگی کلی بدن | بیان شفاهی | قدرت تنه | وضوح گفتار | درک شفاهی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متخصصان تربیت بدنی تطبیقی و اصلاحی | مربیان تخصصی ورزش و سلامت | متخصصان تغذیه و رژیم‌درمانی | فیزیولوژیست‌های ورزشی | هماهنگ‌کنندگان امور تناسب اندام و سلامت | فیزیوتراپ‌ها | مدرسان دانشگاهی تربیت بدنی و علوم ورزشی</t>
+          <t>متخصصان تربیت بدنی انطباقی | مربیان و متخصصان سلامت و توان‌بخشی ورزشی | کارشناسان و متخصصان تغذیه و رژیم‌درمانی | فیزیولوژیست‌های ورزشی | مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | فیزیوتراپیست‌ها | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | تفکر انتقادی | راهبردهای یادگیری | درک مطلب | نگارش | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | تفکر انتقادی | راهبردهای یادگیری | درک مطلب | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | آموزش و تدریس | حقوق و مقررات دولتی | روان‌شناسی | امور اداری و دفتری</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | آموزش و پرورش | قانون و دولت | روان‌شناسی | اداری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | ابتکار و اصالت | روانی و سیالی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدیران مراکز پیش‌دبستانی و مهدکودک‌ها | مدیران امور تفریحی و سرگرمی | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی | هماهنگ‌کنندگان امور تناسب اندام و سلامت | متخصصان تفریح‌درمانی | مربیان و سرپرستان خوابگاه | مدیران خدمات اجتماعی و خدمات شهری</t>
+          <t>مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مدیران مجموعه‌های تفریحی، ورزشی و رویدادها | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | کارشناسان تفریح‌درمانی | سرپرستان و مشاوران خوابگاه | مدیران خدمات اجتماعی و خدمات مردمی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | ایمنی و امنیت عمومی | آموزش و تدریس | درمان و مشاوره | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | ایمنی و امنیت عمومی | آموزش و پرورش | درمان و مشاوره | روان‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مشاوران و کارشناسان هدایت تحصیلی و شغلی | سرپرستان رده‌اول کارکنان خدمات فردی | مشاوران سلامت روان | مراقبان خدمات فردی | کارکنان امور تفریحی و اوقات فراغت | دستیاران خدمات اجتماعی و انسانی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مشاوران تحصیلی، شغلی و هدایت استعدادها | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | مشاوران سلامت روان | مراقبان خدمات شخصی و همراهان توان‌خواهان | کارکنان و متصدیان امور تفریحی و اوقات فراغت | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | روان‌شناسی | آموزش و تدریس | ایمنی و امنیت عمومی | درمان و مشاوره</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی | آموزش و پرورش | ایمنی و امنیت عمومی | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مراقبان خدمات فردی | مراقبان سلامت در منزل | مربیان و مراقبان کودک | سرپرستان و مشاوران خوابگاه | کارکنان امور تفریحی و اوقات فراغت | آرایشگران، متخصصان مو و زیبایی | ماساژورها و ماساژدرمانگران</t>
+          <t>مراقبان خدمات شخصی و همراهان توان‌خواهان | مراقبان سلامت و بهیاران مراقبت در منزل | مربیان و مراقبان کودک | سرپرستان و مشاوران خوابگاه | کارکنان و متصدیان امور تفریحی و اوقات فراغت | آرایشگران و متخصصان زیبایی | ماساژدرمانگران</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | فروش و بازاریابی | آموزش و تدریس | امور اداری و منابع انسانی | اقتصاد و حسابداری</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | فروش و بازاریابی | آموزش و پرورش | پرسنل و منابع انسانی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>وضوح گفتار | درک شفاهی | بیان شفاهی | تشخیص گفتار | حساسیت به مسئله | دید نزدیک | مرتب‌سازی اطلاعات</t>
+          <t>وضوح گفتار | درک شفاهی | بیان شفاهی | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>صندوق‌داران | کارشناسان خدمات مشتریان | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان خدمات فردی | فروشندگان خرده‌فروشی | مدیران فروش | انبارداران و متصدیان جمع‌آوری و چیدمان سفارش‌ها</t>
+          <t>صندوق‌داران | کارشناسان خدمات و پشتیبانی مشتریان | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | فروشندگان خرده‌فروشی | مدیران فروش | متصدیان چیدمان و آماده‌سازی سفارش</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | امور اداری و منابع انسانی | اقتصاد و حسابداری | فروش و بازاریابی | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | پرسنل و منابع انسانی | اقتصاد و حسابداری | فروش و بازاریابی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کارشناسان خدمات مشتریان | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول فروشندگان خرده‌فروشی | کارشناسان منابع انسانی | تحلیل‌گران مدیریت و بهبود فرآیندها | مدیران فروش | کارشناسان فروش خدمات</t>
+          <t>کارشناسان خدمات و پشتیبانی مشتریان | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول فروشندگان خرده‌فروشی | کارشناسان منابع انسانی | کارشناسان تحلیل مدیریت و روش‌ها | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | وضوح گفتار | درک کتبی | حساسیت به مسئله | تشخیص گفتار</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | درک کتبی | حساسیت به مسئله | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متصدیان صدور و ثبت صورت‌حساب | کارمندان پذیرش، باجه و اجاره کالا | کارشناسان خدمات مشتریان | سرپرستان رده‌اول فروشندگان خرده‌فروشی | متصدیان پذیرش و اطلاع‌رسانی | فروشندگان خرده‌فروشی | انبارداران و متصدیان جمع‌آوری و چیدمان سفارش‌ها</t>
+          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | سرپرستان رده‌اول فروشندگان خرده‌فروشی | متصدیان پذیرش و اطلاعات | فروشندگان خرده‌فروشی | متصدیان چیدمان و آماده‌سازی سفارش</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
